--- a/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
@@ -3027,10 +3027,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17129200</v>
+        <v>15631200</v>
       </c>
       <c r="E59" s="3">
-        <v>13795000</v>
+        <v>12499200</v>
       </c>
       <c r="F59" s="3">
         <v>13635600</v>
